--- a/tools/importer/reports/import-landing-page.report.xlsx
+++ b/tools/importer/reports/import-landing-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>landing-page</t>
   </si>
   <si>
-    <t>2026-04-14T22:56:15.302Z</t>
+    <t>2026-04-15T14:45:28.402Z</t>
   </si>
   <si>
     <t>DICK'S Media | Powering Every Win</t>
